--- a/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>SEVN</t>
   </si>
@@ -656,75 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -737,47 +737,50 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E8" s="3">
         <v>18800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>17000</v>
       </c>
       <c r="F8" s="3">
         <v>17000</v>
       </c>
       <c r="G8" s="3">
+        <v>17000</v>
+      </c>
+      <c r="H8" s="3">
         <v>16700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2000</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -790,47 +793,50 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="3">
         <v>10100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>9000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>8800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>700</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,47 +849,50 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E10" s="3">
         <v>8700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8000</v>
-      </c>
-      <c r="F10" s="3">
-        <v>8200</v>
       </c>
       <c r="G10" s="3">
         <v>8200</v>
       </c>
       <c r="H10" s="3">
+        <v>8200</v>
+      </c>
+      <c r="I10" s="3">
         <v>6700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>3300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1300</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -896,8 +905,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,8 +929,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -970,8 +983,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1023,8 +1039,11 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1050,11 +1069,11 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1070,14 +1089,17 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1129,8 +1151,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1147,47 +1172,48 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E17" s="3">
         <v>11300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1600</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1200,47 +1226,50 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E18" s="3">
         <v>7500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>11200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>400</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,8 +1282,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1274,8 +1306,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1312,8 +1345,8 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
@@ -1327,13 +1360,16 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>6200</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>3</v>
@@ -1353,12 +1389,12 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>21000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1380,8 +1416,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1433,47 +1472,50 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E23" s="3">
         <v>7500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1486,13 +1528,16 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1513,19 +1558,19 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -1539,8 +1584,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1592,47 +1640,50 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E26" s="3">
         <v>7500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>20700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>400</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1645,47 +1696,50 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E27" s="3">
         <v>7500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>20700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>400</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1752,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,8 +1808,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1804,8 +1864,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1857,8 +1920,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1910,8 +1976,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1948,8 +2017,8 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
       </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
@@ -1963,47 +2032,50 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E33" s="3">
         <v>7500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>20700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2016,8 +2088,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2069,47 +2144,50 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E35" s="3">
         <v>7500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>20700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,52 +2200,55 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2180,8 +2261,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2201,8 +2285,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2222,47 +2307,48 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>87900</v>
+      </c>
+      <c r="E41" s="3">
         <v>60400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>81800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>84300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>71100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>76400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>48200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>9000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>19300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>46800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,8 +2361,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2328,8 +2417,11 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2375,14 +2467,17 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
+      <c r="R43" s="3">
+        <v>0</v>
       </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2434,47 +2529,50 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E45" s="3">
         <v>6300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2487,8 +2585,11 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2534,53 +2635,56 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
+      <c r="R46" s="3">
+        <v>0</v>
       </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>625700</v>
+      </c>
+      <c r="E47" s="3">
         <v>671500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>628700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>621300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>669900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>695200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>670200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>622700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>572200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>436100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>211400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>147700</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2593,8 +2697,11 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2646,8 +2753,11 @@
       <c r="S48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2699,8 +2809,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2752,8 +2865,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2805,46 +2921,49 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>200</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
       <c r="G52" s="3">
         <v>0</v>
       </c>
       <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
       <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>500</v>
-      </c>
-      <c r="M52" s="3">
-        <v>200</v>
       </c>
       <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>200</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -2852,14 +2971,17 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2911,47 +3033,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>731500</v>
+      </c>
+      <c r="E54" s="3">
         <v>750000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>727900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>706800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>746800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>775200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>721700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>635000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>600000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>456200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>244500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>195100</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2964,8 +3089,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,8 +3113,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3006,47 +3135,48 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E57" s="3">
         <v>4700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1100</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,8 +3189,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3112,28 +3245,31 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2400</v>
-      </c>
-      <c r="G59" s="3">
-        <v>1800</v>
       </c>
       <c r="H59" s="3">
         <v>1800</v>
       </c>
       <c r="I59" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="J59" s="3">
         <v>1100</v>
@@ -3142,17 +3278,17 @@
         <v>1100</v>
       </c>
       <c r="L59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M59" s="3">
         <v>1700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>700</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3165,8 +3301,11 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3212,50 +3351,53 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
+      <c r="R60" s="3">
+        <v>0</v>
       </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>454400</v>
+      </c>
+      <c r="E61" s="3">
         <v>473300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>452700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>433400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>471500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>503500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>452700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>367700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>339600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>215700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>48800</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3271,8 +3413,11 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3318,14 +3463,17 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
+      <c r="R62" s="3">
+        <v>0</v>
       </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3377,8 +3525,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3430,8 +3581,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3483,47 +3637,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>460300</v>
+      </c>
+      <c r="E66" s="3">
         <v>479700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>460100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>439000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>475300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>506800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>455000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>369800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>342300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>219600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1800</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3693,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3557,8 +3717,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3610,8 +3771,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3663,8 +3827,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3716,8 +3883,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3769,47 +3939,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E72" s="3">
         <v>30900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>33100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>30000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>27500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-600</v>
       </c>
-      <c r="M72" s="3">
-        <v>0</v>
-      </c>
       <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
         <v>400</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3822,8 +3995,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3875,8 +4051,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3928,8 +4107,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3981,47 +4163,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>271200</v>
+      </c>
+      <c r="E76" s="3">
         <v>270300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>267800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>267700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>271600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>268400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>266700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>265300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>257700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>236600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>193100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>193200</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4034,8 +4219,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4087,52 +4275,55 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4145,47 +4336,50 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E81" s="3">
         <v>7500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>20700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,8 +4392,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4219,31 +4416,32 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+        <v>300</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -4272,8 +4470,11 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4325,8 +4526,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4378,8 +4582,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4431,8 +4638,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4484,8 +4694,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4537,47 +4750,50 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E89" s="3">
         <v>3300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4590,8 +4806,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4611,8 +4830,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4664,8 +4884,11 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4717,8 +4940,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4770,47 +4996,50 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-39900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>50300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>27800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-44900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-44600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-116800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-49000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-63000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-55000</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +5052,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4844,8 +5076,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4853,32 +5086,32 @@
         <v>-5200</v>
       </c>
       <c r="E96" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="F96" s="3">
         <v>-5100</v>
       </c>
       <c r="G96" s="3">
-        <v>-3700</v>
+        <v>-5100</v>
       </c>
       <c r="H96" s="3">
         <v>-3700</v>
       </c>
       <c r="I96" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="J96" s="3">
         <v>-3600</v>
       </c>
       <c r="K96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-3100</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -4897,8 +5130,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4950,8 +5186,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5003,8 +5242,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5056,47 +5298,50 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E100" s="3">
         <v>15000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>13800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-43600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-36000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>46700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>81100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>24200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>123700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>34900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>47300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5109,8 +5354,11 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5162,47 +5410,50 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-21500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>28000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>39400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-16500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-56500</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5213,6 +5464,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
   <si>
     <t>SEVN</t>
   </si>
@@ -656,78 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -740,50 +741,53 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E8" s="3">
         <v>18900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18800</v>
-      </c>
-      <c r="F8" s="3">
-        <v>17000</v>
       </c>
       <c r="G8" s="3">
         <v>17000</v>
       </c>
       <c r="H8" s="3">
+        <v>17000</v>
+      </c>
+      <c r="I8" s="3">
         <v>16700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>15500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>26100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2000</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -796,50 +800,53 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E9" s="3">
         <v>10000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>9000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>8800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>700</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -852,50 +859,53 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E10" s="3">
         <v>8900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>8200</v>
       </c>
       <c r="H10" s="3">
         <v>8200</v>
       </c>
       <c r="I10" s="3">
+        <v>8200</v>
+      </c>
+      <c r="J10" s="3">
         <v>6700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>23500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -908,8 +918,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -930,8 +943,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -986,8 +1000,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1042,13 +1059,16 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1072,11 +1092,11 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1092,14 +1112,17 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1154,8 +1177,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1173,50 +1199,51 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E17" s="3">
         <v>13000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>9200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1600</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1229,50 +1256,53 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E18" s="3">
         <v>5900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>20900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>400</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1285,8 +1315,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1307,8 +1340,9 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1348,8 +1382,8 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1363,17 +1397,20 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E21" s="3">
         <v>6200</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1392,12 +1429,12 @@
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>21000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1419,8 +1456,11 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1475,50 +1515,53 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E23" s="3">
         <v>5900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>7500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>6800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>11200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>21000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1531,17 +1574,20 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -1561,19 +1607,19 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>300</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1587,8 +1633,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1643,50 +1692,53 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E26" s="3">
         <v>6000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>20700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>400</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,50 +1751,53 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E27" s="3">
         <v>6000</v>
       </c>
-      <c r="E27" s="3">
-        <v>7500</v>
-      </c>
       <c r="F27" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G27" s="3">
         <v>4600</v>
       </c>
-      <c r="G27" s="3">
-        <v>7800</v>
-      </c>
       <c r="H27" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I27" s="3">
         <v>6800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>20700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1755,8 +1810,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1811,8 +1869,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1867,8 +1928,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1923,8 +1987,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1979,8 +2046,11 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2020,8 +2090,8 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -2035,50 +2105,53 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E33" s="3">
         <v>6000</v>
       </c>
-      <c r="E33" s="3">
-        <v>7500</v>
-      </c>
       <c r="F33" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G33" s="3">
         <v>4600</v>
       </c>
-      <c r="G33" s="3">
-        <v>7800</v>
-      </c>
       <c r="H33" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I33" s="3">
         <v>6800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>20700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2091,8 +2164,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2147,50 +2223,53 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E35" s="3">
         <v>6000</v>
       </c>
-      <c r="E35" s="3">
-        <v>7500</v>
-      </c>
       <c r="F35" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G35" s="3">
         <v>4600</v>
       </c>
-      <c r="G35" s="3">
-        <v>7800</v>
-      </c>
       <c r="H35" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I35" s="3">
         <v>6800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>20700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2203,55 +2282,58 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2264,8 +2346,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2286,8 +2371,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2308,50 +2394,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>93300</v>
+      </c>
+      <c r="E41" s="3">
         <v>87900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>60400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>81800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>84300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>76400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>48200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>9000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>19300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>46800</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2364,8 +2451,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2420,8 +2510,11 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2470,14 +2563,17 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2532,8 +2628,11 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2541,41 +2640,41 @@
         <v>2500</v>
       </c>
       <c r="E45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F45" s="3">
         <v>6300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2588,8 +2687,11 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2638,56 +2740,59 @@
       <c r="R46" s="3">
         <v>0</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
+      <c r="S46" s="3">
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>586900</v>
+      </c>
+      <c r="E47" s="3">
         <v>625700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>671500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>628700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>621300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>669900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>695200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>670200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>622700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>572200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>436100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>211400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>147700</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2700,8 +2805,11 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2756,8 +2864,11 @@
       <c r="T48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2812,8 +2923,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2868,8 +2982,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2924,49 +3041,52 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
       <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>500</v>
-      </c>
-      <c r="N52" s="3">
-        <v>200</v>
       </c>
       <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>200</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -2974,14 +3094,17 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3036,50 +3159,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>697700</v>
+      </c>
+      <c r="E54" s="3">
         <v>731500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>750000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>727900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>706800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>746800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>775200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>721700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>635000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>600000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>456200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>244500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>195100</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3092,8 +3218,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3114,8 +3243,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3136,50 +3266,51 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E57" s="3">
         <v>3800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3192,31 +3323,34 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
+        <v>157100</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -3248,31 +3382,34 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
         <v>2000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>1800</v>
       </c>
       <c r="I59" s="3">
         <v>1800</v>
       </c>
       <c r="J59" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="K59" s="3">
         <v>1100</v>
@@ -3281,17 +3418,17 @@
         <v>1100</v>
       </c>
       <c r="M59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="N59" s="3">
         <v>1700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>700</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,8 +3441,11 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3354,53 +3494,56 @@
       <c r="R60" s="3">
         <v>0</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="S60" s="3">
+        <v>0</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>264100</v>
+      </c>
+      <c r="E61" s="3">
         <v>454400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>473300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>452700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>433400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>471500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>503500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>452700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>367700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>339600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>215700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>48800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3416,8 +3559,11 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3466,14 +3612,17 @@
       <c r="R62" s="3">
         <v>0</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
+      <c r="S62" s="3">
+        <v>0</v>
       </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3528,8 +3677,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3584,8 +3736,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3640,50 +3795,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>426200</v>
+      </c>
+      <c r="E66" s="3">
         <v>460300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>479700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>460100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>439000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>475300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>506800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>455000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>369800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>342300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>219600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>51400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1800</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3696,8 +3854,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3718,8 +3879,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3774,8 +3936,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3830,8 +3995,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3886,8 +4054,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3942,8 +4113,11 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3951,41 +4125,41 @@
         <v>31800</v>
       </c>
       <c r="E72" s="3">
+        <v>31800</v>
+      </c>
+      <c r="F72" s="3">
         <v>30900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>28600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>29100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>33100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>30000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>28500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-600</v>
       </c>
-      <c r="N72" s="3">
-        <v>0</v>
-      </c>
       <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3">
         <v>400</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3998,8 +4172,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4054,8 +4231,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4110,8 +4290,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4166,50 +4349,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>271600</v>
+      </c>
+      <c r="E76" s="3">
         <v>271200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>270300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>267800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>267700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>271600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>268400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>266700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>265300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>257700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>236600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>193100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>193200</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4222,8 +4408,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4278,55 +4467,58 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4339,50 +4531,53 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E81" s="3">
         <v>6000</v>
       </c>
-      <c r="E81" s="3">
-        <v>7500</v>
-      </c>
       <c r="F81" s="3">
+        <v>7400</v>
+      </c>
+      <c r="G81" s="3">
         <v>4600</v>
       </c>
-      <c r="G81" s="3">
-        <v>7800</v>
-      </c>
       <c r="H81" s="3">
+        <v>7700</v>
+      </c>
+      <c r="I81" s="3">
         <v>6800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>20700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4395,8 +4590,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4417,17 +4615,18 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>400</v>
+      </c>
+      <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4443,8 +4642,8 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -4473,8 +4672,11 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4529,8 +4731,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4585,8 +4790,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4641,8 +4849,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4697,8 +4908,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4753,50 +4967,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E89" s="3">
         <v>5300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4809,8 +5026,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4831,8 +5051,9 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4887,8 +5108,11 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4943,8 +5167,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4999,50 +5226,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>39600</v>
+      </c>
+      <c r="E94" s="3">
         <v>46500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-39900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>50300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>27800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-22400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-44900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-44600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-116800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-49000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-63000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-55000</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5055,8 +5285,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5077,8 +5310,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5089,32 +5323,32 @@
         <v>-5200</v>
       </c>
       <c r="F96" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="G96" s="3">
         <v>-5100</v>
       </c>
       <c r="H96" s="3">
-        <v>-3700</v>
+        <v>-5100</v>
       </c>
       <c r="I96" s="3">
         <v>-3700</v>
       </c>
       <c r="J96" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="K96" s="3">
         <v>-3600</v>
       </c>
       <c r="L96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-3100</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -5133,8 +5367,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5189,8 +5426,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5245,8 +5485,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5301,50 +5544,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-24500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>15000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>13800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-43600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-36000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>46700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>81100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>24200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>123700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>34900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>47300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5357,8 +5603,11 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5413,50 +5662,53 @@
       <c r="T101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E102" s="3">
         <v>27300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-21500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>13200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>28000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>39400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-16500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-56500</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5467,6 +5719,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>SEVN</t>
   </si>
@@ -656,82 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -744,53 +745,56 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E8" s="3">
         <v>18000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>18900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>18800</v>
-      </c>
-      <c r="G8" s="3">
-        <v>17000</v>
       </c>
       <c r="H8" s="3">
         <v>17000</v>
       </c>
       <c r="I8" s="3">
+        <v>17000</v>
+      </c>
+      <c r="J8" s="3">
         <v>16700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>13200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>10500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>26100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2000</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,53 +807,56 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E9" s="3">
         <v>9800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>10000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>10100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>700</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -862,53 +869,56 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E10" s="3">
         <v>8200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>8900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8000</v>
-      </c>
-      <c r="H10" s="3">
-        <v>8200</v>
       </c>
       <c r="I10" s="3">
         <v>8200</v>
       </c>
       <c r="J10" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K10" s="3">
         <v>6700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>12700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>23500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>2200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +931,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,8 +957,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1003,8 +1017,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,16 +1079,19 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1095,11 +1115,11 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1115,14 +1135,17 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1180,8 +1203,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1200,53 +1226,54 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E17" s="3">
         <v>12800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>9200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1600</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,53 +1286,56 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E18" s="3">
         <v>5200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>20900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1348,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1341,8 +1374,9 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1385,8 +1419,8 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
@@ -1400,20 +1434,23 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E21" s="3">
         <v>5600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6200</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1432,12 +1469,12 @@
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
         <v>21000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,8 +1496,11 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1518,53 +1558,56 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E23" s="3">
         <v>5200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,8 +1620,11 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1586,11 +1632,11 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
         <v>0</v>
       </c>
@@ -1610,19 +1656,19 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -1636,8 +1682,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1695,53 +1744,56 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E26" s="3">
         <v>5200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>6000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,53 +1806,56 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E27" s="3">
         <v>5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1813,8 +1868,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1872,8 +1930,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1931,8 +1992,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,8 +2054,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2049,8 +2116,11 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2093,8 +2163,8 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
@@ -2108,53 +2178,56 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E33" s="3">
         <v>5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,8 +2240,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2226,53 +2302,56 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E35" s="3">
         <v>5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,58 +2364,61 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2349,8 +2431,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,8 +2457,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,53 +2481,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E41" s="3">
         <v>93300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>87900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>60400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>81800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>84300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>71100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>76400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>48200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>19300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>30400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>46800</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2454,8 +2541,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2513,8 +2603,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2566,14 +2659,17 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
+      <c r="T43" s="3">
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2631,53 +2727,56 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>2500</v>
+        <v>3600</v>
       </c>
       <c r="E45" s="3">
         <v>2500</v>
       </c>
       <c r="F45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G45" s="3">
         <v>6300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,8 +2789,11 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2743,59 +2845,62 @@
       <c r="S46" s="3">
         <v>0</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
+      <c r="T46" s="3">
+        <v>0</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>606800</v>
+      </c>
+      <c r="E47" s="3">
         <v>586900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>625700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>671500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>628700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>621300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>669900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>695200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>670200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>622700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>572200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>436100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>211400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>147700</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2808,8 +2913,11 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2867,8 +2975,11 @@
       <c r="U48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2926,8 +3037,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2985,8 +3099,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3044,8 +3161,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3055,41 +3175,41 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
       <c r="I52" s="3">
         <v>0</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>500</v>
-      </c>
-      <c r="O52" s="3">
-        <v>200</v>
       </c>
       <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>200</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
@@ -3097,14 +3217,17 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T52" s="3">
-        <v>0</v>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3162,53 +3285,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>694900</v>
+      </c>
+      <c r="E54" s="3">
         <v>697700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>731500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>750000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>727900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>706800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>746800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>775200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>721700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>635000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>600000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>456200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>244500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>195100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,8 +3347,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3244,8 +3373,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3267,53 +3397,54 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E57" s="3">
         <v>3700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,16 +3457,19 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
         <v>157100</v>
       </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+      <c r="E58" s="3">
+        <v>157100</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>3</v>
@@ -3352,8 +3486,8 @@
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -3385,34 +3519,37 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>1800</v>
       </c>
       <c r="J59" s="3">
         <v>1800</v>
       </c>
       <c r="K59" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="L59" s="3">
         <v>1100</v>
@@ -3421,17 +3558,17 @@
         <v>1100</v>
       </c>
       <c r="N59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="O59" s="3">
         <v>1700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>700</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,8 +3581,11 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3497,56 +3637,59 @@
       <c r="S60" s="3">
         <v>0</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
+      <c r="T60" s="3">
+        <v>0</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>260900</v>
+      </c>
+      <c r="E61" s="3">
         <v>264100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>454400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>473300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>452700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>433400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>471500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>503500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>452700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>367700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>339600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>215700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>48800</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3562,8 +3705,11 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3615,14 +3761,17 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
+      <c r="T62" s="3">
+        <v>0</v>
       </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,8 +3829,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3739,8 +3891,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3798,53 +3953,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>423800</v>
+      </c>
+      <c r="E66" s="3">
         <v>426200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>460300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>479700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>460100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>439000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>475300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>506800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>455000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>369800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>342300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>219600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>51400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1800</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +4015,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3880,8 +4041,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3939,8 +4101,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3998,8 +4163,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4057,8 +4225,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4116,53 +4287,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>31800</v>
+        <v>30900</v>
       </c>
       <c r="E72" s="3">
         <v>31800</v>
       </c>
       <c r="F72" s="3">
+        <v>31800</v>
+      </c>
+      <c r="G72" s="3">
         <v>30900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>33100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>30000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>20100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-600</v>
       </c>
-      <c r="O72" s="3">
-        <v>0</v>
-      </c>
       <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3">
         <v>400</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4349,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4234,8 +4411,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4293,8 +4473,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4352,53 +4535,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>271100</v>
+      </c>
+      <c r="E76" s="3">
         <v>271600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>271200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>270300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>267800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>267700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>271600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>268400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>266700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>265300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>257700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>236600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>193100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>193200</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,8 +4597,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4470,58 +4659,61 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4534,53 +4726,56 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E81" s="3">
         <v>5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4593,8 +4788,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4616,20 +4814,21 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4645,8 +4844,8 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M83" s="3">
         <v>0</v>
@@ -4675,8 +4874,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4734,8 +4936,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4793,8 +4998,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4852,8 +5060,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4911,8 +5122,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4970,53 +5184,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E89" s="3">
         <v>4700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5029,8 +5246,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5052,8 +5272,9 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5111,8 +5332,11 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5170,8 +5394,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5229,53 +5456,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E94" s="3">
         <v>39600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>46500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-39900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>50300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>27800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-44900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-44600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-116800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-49000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-63000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-55000</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5288,8 +5518,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5311,8 +5544,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5326,32 +5560,32 @@
         <v>-5200</v>
       </c>
       <c r="G96" s="3">
-        <v>-5100</v>
+        <v>-5200</v>
       </c>
       <c r="H96" s="3">
         <v>-5100</v>
       </c>
       <c r="I96" s="3">
-        <v>-3700</v>
+        <v>-5100</v>
       </c>
       <c r="J96" s="3">
         <v>-3700</v>
       </c>
       <c r="K96" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="L96" s="3">
         <v>-3600</v>
       </c>
       <c r="M96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-3100</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -5370,8 +5604,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5429,8 +5666,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5488,8 +5728,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5547,53 +5790,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-38800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-24500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>15000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>13800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-43600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-36000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>46700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>81100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>24200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>123700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>34900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>47300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5606,8 +5852,11 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5665,53 +5914,56 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="E102" s="3">
         <v>5400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>27300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-21500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>13200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>28000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>39400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-16500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-56500</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5722,6 +5974,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
   <si>
     <t>SEVN</t>
   </si>
@@ -656,86 +656,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -748,56 +749,59 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>17800</v>
+        <v>6900</v>
       </c>
       <c r="E8" s="3">
-        <v>18000</v>
+        <v>7300</v>
       </c>
       <c r="F8" s="3">
-        <v>18900</v>
+        <v>7500</v>
       </c>
       <c r="G8" s="3">
-        <v>18800</v>
+        <v>8700</v>
       </c>
       <c r="H8" s="3">
-        <v>17000</v>
+        <v>10100</v>
       </c>
       <c r="I8" s="3">
-        <v>17000</v>
+        <v>7000</v>
       </c>
       <c r="J8" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K8" s="3">
         <v>16700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>15500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>26100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2000</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,56 +814,59 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>9500</v>
+        <v>600</v>
       </c>
       <c r="E9" s="3">
-        <v>9800</v>
+        <v>600</v>
       </c>
       <c r="F9" s="3">
-        <v>10000</v>
+        <v>600</v>
       </c>
       <c r="G9" s="3">
-        <v>10100</v>
+        <v>600</v>
       </c>
       <c r="H9" s="3">
-        <v>9000</v>
+        <v>500</v>
       </c>
       <c r="I9" s="3">
-        <v>8800</v>
-      </c>
-      <c r="J9" s="3">
+        <v>200</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3">
         <v>8500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>4100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>700</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,56 +879,59 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>8300</v>
+        <v>6300</v>
       </c>
       <c r="E10" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F10" s="3">
+        <v>6900</v>
+      </c>
+      <c r="G10" s="3">
+        <v>8100</v>
+      </c>
+      <c r="H10" s="3">
+        <v>9500</v>
+      </c>
+      <c r="I10" s="3">
+        <v>6800</v>
+      </c>
+      <c r="J10" s="3">
+        <v>9100</v>
+      </c>
+      <c r="K10" s="3">
         <v>8200</v>
       </c>
-      <c r="F10" s="3">
-        <v>8900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>8700</v>
-      </c>
-      <c r="H10" s="3">
-        <v>8000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>8200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>8200</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>12700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>23500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>3300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1300</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -934,8 +944,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -958,8 +971,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1020,8 +1034,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1082,8 +1099,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1093,20 +1113,20 @@
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1118,11 +1138,11 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1138,31 +1158,34 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1206,8 +1229,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1227,56 +1253,57 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13500</v>
+        <v>3400</v>
       </c>
       <c r="E17" s="3">
-        <v>12800</v>
+        <v>3000</v>
       </c>
       <c r="F17" s="3">
-        <v>13000</v>
+        <v>2300</v>
       </c>
       <c r="G17" s="3">
-        <v>11300</v>
+        <v>2700</v>
       </c>
       <c r="H17" s="3">
-        <v>12300</v>
+        <v>2600</v>
       </c>
       <c r="I17" s="3">
-        <v>9200</v>
+        <v>2300</v>
       </c>
       <c r="J17" s="3">
+        <v>1300</v>
+      </c>
+      <c r="K17" s="3">
         <v>10000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1600</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1289,56 +1316,59 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4300</v>
+        <v>3500</v>
       </c>
       <c r="E18" s="3">
+        <v>4200</v>
+      </c>
+      <c r="F18" s="3">
         <v>5200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>20900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>400</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1351,8 +1381,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1375,31 +1408,32 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1422,8 +1456,8 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1437,31 +1471,34 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E21" s="3">
         <v>4600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5600</v>
       </c>
-      <c r="F21" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="G21" s="3">
+        <v>6800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I21" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J21" s="3">
+        <v>7800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1472,12 +1509,12 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>21000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1499,31 +1536,34 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1561,56 +1601,59 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E23" s="3">
         <v>4200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>6800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1623,8 +1666,11 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1635,11 +1681,11 @@
         <v>0</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
@@ -1659,19 +1705,19 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
+      <c r="R24" s="3">
+        <v>0</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
@@ -1685,8 +1731,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1747,56 +1796,59 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E26" s="3">
         <v>4200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>6800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,56 +1861,59 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E27" s="3">
         <v>4200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>5200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>6000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>6800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>20700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1871,8 +1926,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1933,8 +1991,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1995,8 +2056,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2057,8 +2121,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2119,31 +2186,34 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -2166,8 +2236,8 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2181,56 +2251,59 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E33" s="3">
         <v>4200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>5200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>6000</v>
       </c>
-      <c r="G33" s="3">
-        <v>7400</v>
-      </c>
       <c r="H33" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I33" s="3">
         <v>4600</v>
       </c>
-      <c r="I33" s="3">
-        <v>7700</v>
-      </c>
       <c r="J33" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K33" s="3">
         <v>6800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>20700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2243,8 +2316,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2305,56 +2381,59 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E35" s="3">
         <v>4200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>5200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>6000</v>
       </c>
-      <c r="G35" s="3">
-        <v>7400</v>
-      </c>
       <c r="H35" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I35" s="3">
         <v>4600</v>
       </c>
-      <c r="I35" s="3">
-        <v>7700</v>
-      </c>
       <c r="J35" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K35" s="3">
         <v>6800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>20700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,61 +2446,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2516,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2458,8 +2543,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2482,56 +2568,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>82200</v>
+      </c>
+      <c r="E41" s="3">
         <v>69600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>93300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>87900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>60400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>81800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>84300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>71100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>76400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>48200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>19300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>30400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>46800</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2544,8 +2631,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2606,31 +2696,34 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>554000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>607800</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>587800</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>626400</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>671800</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>628800</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>621300</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2662,37 +2755,40 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+      <c r="U43" s="3">
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2730,56 +2826,59 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3600</v>
+        <v>1600</v>
       </c>
       <c r="E45" s="3">
         <v>2500</v>
       </c>
       <c r="F45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>500</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K45" s="3">
+        <v>5900</v>
+      </c>
+      <c r="L45" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N45" s="3">
+        <v>3400</v>
+      </c>
+      <c r="O45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q45" s="3">
         <v>2500</v>
       </c>
-      <c r="G45" s="3">
-        <v>6300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J45" s="3">
-        <v>5900</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3600</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="M45" s="3">
-        <v>3400</v>
-      </c>
-      <c r="N45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="P45" s="3">
-        <v>2500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>300</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,31 +2891,34 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>637900</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>679900</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>682600</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>714800</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>733400</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>712300</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>706800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2848,62 +2950,65 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
+      <c r="U46" s="3">
+        <v>0</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>606800</v>
-      </c>
-      <c r="E47" s="3">
-        <v>586900</v>
-      </c>
-      <c r="F47" s="3">
-        <v>625700</v>
-      </c>
-      <c r="G47" s="3">
-        <v>671500</v>
-      </c>
-      <c r="H47" s="3">
-        <v>628700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>621300</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>669900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>695200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>670200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>622700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>572200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>436100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>211400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>147700</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2916,31 +3021,34 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -2978,8 +3086,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3040,8 +3151,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3102,8 +3216,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3164,55 +3281,58 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F52" s="3">
+        <v>15100</v>
       </c>
       <c r="G52" s="3">
+        <v>16800</v>
+      </c>
+      <c r="H52" s="3">
+        <v>16600</v>
+      </c>
+      <c r="I52" s="3">
+        <v>15600</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
-        <v>200</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>100</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>500</v>
-      </c>
-      <c r="P52" s="3">
-        <v>200</v>
       </c>
       <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="R52" s="3">
+        <v>200</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3220,14 +3340,17 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3288,56 +3411,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>652600</v>
+      </c>
+      <c r="E54" s="3">
         <v>694900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>697700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>731500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>750000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>727900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>706800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>746800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>775200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>721700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>635000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>600000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>456200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>244500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>195100</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3476,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3374,8 +3503,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3398,56 +3528,57 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>4400</v>
+        <v>2700</v>
       </c>
       <c r="E57" s="3">
-        <v>3700</v>
+        <v>2200</v>
       </c>
       <c r="F57" s="3">
-        <v>3800</v>
+        <v>2400</v>
       </c>
       <c r="G57" s="3">
-        <v>4700</v>
+        <v>3300</v>
       </c>
       <c r="H57" s="3">
-        <v>4300</v>
+        <v>3900</v>
       </c>
       <c r="I57" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3460,37 +3591,40 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>157100</v>
+        <v>213300</v>
       </c>
       <c r="E58" s="3">
-        <v>157100</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>330300</v>
+      </c>
+      <c r="F58" s="3">
+        <v>333600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -3522,37 +3656,40 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1200</v>
       </c>
-      <c r="F59" s="3">
-        <v>2000</v>
-      </c>
       <c r="G59" s="3">
-        <v>1700</v>
+        <v>2600</v>
       </c>
       <c r="H59" s="3">
-        <v>3100</v>
+        <v>2400</v>
       </c>
       <c r="I59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J59" s="3">
         <v>2400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1800</v>
       </c>
       <c r="K59" s="3">
         <v>1800</v>
       </c>
       <c r="L59" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="M59" s="3">
         <v>1100</v>
@@ -3561,17 +3698,17 @@
         <v>1100</v>
       </c>
       <c r="O59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="P59" s="3">
         <v>1700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>700</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3584,31 +3721,34 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>218400</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>334100</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>337300</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>5900</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>5600</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3640,59 +3780,62 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
+      <c r="U60" s="3">
+        <v>0</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>260900</v>
+        <v>162600</v>
       </c>
       <c r="E61" s="3">
-        <v>264100</v>
+        <v>87600</v>
       </c>
       <c r="F61" s="3">
+        <v>87500</v>
+      </c>
+      <c r="G61" s="3">
         <v>454400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>473300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>452700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>433400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>471500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>503500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>452700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>367700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>339600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>215700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>48800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3708,31 +3851,34 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>2100</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+        <v>1400</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -3764,14 +3910,17 @@
       <c r="T62" s="3">
         <v>0</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
+      <c r="U62" s="3">
+        <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3832,8 +3981,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3894,8 +4046,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3956,56 +4111,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>383100</v>
+      </c>
+      <c r="E66" s="3">
         <v>423800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>426200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>460300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>479700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>460100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>439000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>475300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>506800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>455000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>369800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>342300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>219600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>51400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1800</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4018,8 +4176,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4042,8 +4203,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4104,8 +4266,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4166,8 +4331,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4228,8 +4396,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4290,56 +4461,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E72" s="3">
         <v>30900</v>
-      </c>
-      <c r="E72" s="3">
-        <v>31800</v>
       </c>
       <c r="F72" s="3">
         <v>31800</v>
       </c>
       <c r="G72" s="3">
+        <v>31800</v>
+      </c>
+      <c r="H72" s="3">
         <v>30900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>29100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>33100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>30000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>28500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>20100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-600</v>
       </c>
-      <c r="P72" s="3">
-        <v>0</v>
-      </c>
       <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3">
         <v>400</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4352,8 +4526,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4414,8 +4591,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4476,8 +4656,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4538,56 +4721,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>269500</v>
+      </c>
+      <c r="E76" s="3">
         <v>271100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>271600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>271200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>270300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>267800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>267700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>271600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>268400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>266700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>265300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>257700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>236600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>193100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>193200</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4600,8 +4786,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4662,61 +4851,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4729,56 +4921,59 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E81" s="3">
         <v>4200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>5200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>6000</v>
       </c>
-      <c r="G81" s="3">
-        <v>7400</v>
-      </c>
       <c r="H81" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I81" s="3">
         <v>4600</v>
       </c>
-      <c r="I81" s="3">
-        <v>7700</v>
-      </c>
       <c r="J81" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K81" s="3">
         <v>6800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>20700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,8 +4986,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4815,19 +5013,20 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3">
-        <v>400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>300</v>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -4847,8 +5046,8 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3">
         <v>0</v>
@@ -4877,8 +5076,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4939,8 +5141,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5001,8 +5206,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5063,8 +5271,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5125,8 +5336,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5187,56 +5401,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E89" s="3">
         <v>4200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1400</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5249,8 +5466,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5273,31 +5493,32 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -5335,8 +5556,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5397,8 +5621,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5459,56 +5686,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>39600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>46500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-39900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>50300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>27800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-44900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-44600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-116800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-49000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-63000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-55000</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5521,8 +5751,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5545,50 +5778,51 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-5200</v>
+        <v>5200</v>
       </c>
       <c r="E96" s="3">
-        <v>-5200</v>
+        <v>5200</v>
       </c>
       <c r="F96" s="3">
-        <v>-5200</v>
+        <v>5200</v>
       </c>
       <c r="G96" s="3">
-        <v>-5200</v>
+        <v>5200</v>
       </c>
       <c r="H96" s="3">
-        <v>-5100</v>
+        <v>5200</v>
       </c>
       <c r="I96" s="3">
-        <v>-5100</v>
+        <v>5100</v>
       </c>
       <c r="J96" s="3">
-        <v>-3700</v>
+        <v>5100</v>
       </c>
       <c r="K96" s="3">
         <v>-3700</v>
       </c>
       <c r="L96" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="M96" s="3">
         <v>-3600</v>
       </c>
       <c r="N96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-3100</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -5607,8 +5841,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5669,8 +5906,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5731,8 +5971,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5793,56 +6036,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-8800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-38800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-24500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>15000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>13800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-43600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-36000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>46700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>81100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>24200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>123700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>34900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>47300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5855,31 +6101,34 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -5917,56 +6166,59 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-23700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>27300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-21500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>13200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>28000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>39400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-56500</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5977,6 +6229,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="92">
   <si>
     <t>SEVN</t>
   </si>
@@ -656,90 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,59 +752,62 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E8" s="3">
         <v>6900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>26100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2000</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -817,8 +820,11 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -835,41 +841,41 @@
         <v>600</v>
       </c>
       <c r="H9" s="3">
+        <v>600</v>
+      </c>
+      <c r="I9" s="3">
         <v>500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>200</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L9" s="3">
         <v>8500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>4100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>700</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,59 +888,62 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E10" s="3">
         <v>6300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>23500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>3300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -947,8 +956,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +984,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1037,8 +1050,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,8 +1118,11 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1128,8 +1147,8 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1141,11 +1160,11 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1161,14 +1180,17 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1179,17 +1201,17 @@
         <v>300</v>
       </c>
       <c r="F15" s="3">
+        <v>300</v>
+      </c>
+      <c r="G15" s="3">
         <v>400</v>
       </c>
-      <c r="G15" s="3">
-        <v>900</v>
-      </c>
       <c r="H15" s="3">
+        <v>300</v>
+      </c>
+      <c r="I15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
@@ -1232,8 +1254,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,59 +1279,60 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E17" s="3">
         <v>3400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1600</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1319,59 +1345,62 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E18" s="3">
         <v>3500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>400</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1413,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,8 +1441,9 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1435,8 +1468,8 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1459,8 +1492,8 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
       </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
@@ -1474,35 +1507,38 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E21" s="3">
         <v>3800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>5600</v>
       </c>
-      <c r="G21" s="3">
-        <v>6800</v>
-      </c>
       <c r="H21" s="3">
+        <v>6200</v>
+      </c>
+      <c r="I21" s="3">
         <v>7600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1512,12 +1548,12 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3">
         <v>21000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1575,11 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1565,8 +1604,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1604,59 +1643,62 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E23" s="3">
         <v>3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>11200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>21000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>400</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1669,8 +1711,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1684,11 +1729,11 @@
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -1708,19 +1753,19 @@
         <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>300</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
-      </c>
       <c r="Q24" s="3">
         <v>0</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -1734,8 +1779,11 @@
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,59 +1847,62 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E26" s="3">
         <v>3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>20700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,59 +1915,62 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E27" s="3">
         <v>3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>20700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1929,8 +1983,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2051,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2119,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2187,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,8 +2255,11 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2215,8 +2284,8 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2239,8 +2308,8 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
       </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
@@ -2254,59 +2323,62 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E33" s="3">
         <v>3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>20700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2391,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,59 +2459,62 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E35" s="3">
         <v>3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>20700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2449,64 +2527,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2600,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2628,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,59 +2654,60 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>70800</v>
+      </c>
+      <c r="E41" s="3">
         <v>82200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>69600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>93300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>87900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>60400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>81800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>84300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>71100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>76400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>48200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>26200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>30400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>46800</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2634,8 +2720,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2699,35 +2788,38 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>605900</v>
+      </c>
+      <c r="E43" s="3">
         <v>554000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>607800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>587800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>626400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>671800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>628800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>621300</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -2758,14 +2850,17 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
+      <c r="V43" s="3">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2790,8 +2885,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2829,59 +2924,62 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
-        <v>500</v>
-      </c>
       <c r="H45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I45" s="3">
         <v>1000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,35 +2992,38 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>677500</v>
+      </c>
+      <c r="E46" s="3">
         <v>637900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>679900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>682600</v>
       </c>
-      <c r="G46" s="3">
-        <v>714800</v>
-      </c>
       <c r="H46" s="3">
+        <v>715400</v>
+      </c>
+      <c r="I46" s="3">
         <v>733400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>712300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>706800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2953,14 +3054,17 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
+      <c r="V46" s="3">
+        <v>0</v>
       </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2985,33 +3089,33 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>669900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>695200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>670200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>622700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>572200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>436100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>211400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>147700</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3024,8 +3128,11 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3050,8 +3157,8 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -3089,8 +3196,11 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3154,8 +3264,11 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3332,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,58 +3400,61 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E52" s="3">
         <v>14700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15100</v>
       </c>
-      <c r="G52" s="3">
-        <v>16800</v>
-      </c>
       <c r="H52" s="3">
+        <v>16100</v>
+      </c>
+      <c r="I52" s="3">
         <v>16600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15600</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
       <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>500</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>200</v>
       </c>
       <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
+      <c r="S52" s="3">
+        <v>200</v>
       </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
@@ -3343,14 +3462,17 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,59 +3536,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>692800</v>
+      </c>
+      <c r="E54" s="3">
         <v>652600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>694900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>697700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>731500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>750000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>727900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>706800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>746800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>775200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>721700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>635000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>600000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>456200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>244500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>195100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3604,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3632,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,59 +3658,60 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,23 +3724,26 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>255800</v>
+      </c>
+      <c r="E58" s="3">
         <v>213300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>330300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>333600</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
@@ -3620,14 +3753,14 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -3659,40 +3792,43 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E59" s="3">
         <v>2400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2400</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1800</v>
       </c>
       <c r="L59" s="3">
         <v>1800</v>
       </c>
       <c r="M59" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="N59" s="3">
         <v>1100</v>
@@ -3701,17 +3837,17 @@
         <v>1100</v>
       </c>
       <c r="P59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="Q59" s="3">
         <v>1700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>700</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3724,35 +3860,38 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>261500</v>
+      </c>
+      <c r="E60" s="3">
         <v>218400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>334100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>337300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>5900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5600</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -3783,62 +3922,65 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
+      <c r="V60" s="3">
+        <v>0</v>
       </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E61" s="3">
         <v>162600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>87600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>87500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>454400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>473300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>452700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>433400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>471500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>503500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>452700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>367700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>339600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>215700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>48800</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3854,23 +3996,26 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>2100</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E62" s="3">
         <v>2100</v>
       </c>
       <c r="F62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="G62" s="3">
         <v>1400</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3880,8 +4025,8 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -3913,14 +4058,17 @@
       <c r="U62" s="3">
         <v>0</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
+      <c r="V62" s="3">
+        <v>0</v>
       </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4132,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4200,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,59 +4268,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>423500</v>
+      </c>
+      <c r="E66" s="3">
         <v>383100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>423800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>426200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>460300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>479700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>460100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>439000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>475300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>506800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>455000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>369800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>342300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>219600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>51400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1800</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4179,8 +4336,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4364,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4430,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4498,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4566,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,59 +4634,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E72" s="3">
         <v>29200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>30900</v>
-      </c>
-      <c r="F72" s="3">
-        <v>31800</v>
       </c>
       <c r="G72" s="3">
         <v>31800</v>
       </c>
       <c r="H72" s="3">
+        <v>31800</v>
+      </c>
+      <c r="I72" s="3">
         <v>30900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>28600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>29100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>33100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>30000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>20100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-600</v>
       </c>
-      <c r="Q72" s="3">
-        <v>0</v>
-      </c>
       <c r="R72" s="3">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3">
         <v>400</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4529,8 +4702,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4770,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4838,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,59 +4906,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>269300</v>
+      </c>
+      <c r="E76" s="3">
         <v>269500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>271100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>271600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>271200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>270300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>267800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>267700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>271600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>268400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>266700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>265300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>257700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>236600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>193100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>193200</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4789,8 +4974,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,64 +5042,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,59 +5115,62 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E81" s="3">
         <v>3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>20700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4989,8 +5183,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,16 +5211,17 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
         <v>300</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="E83" s="3">
+        <v>300</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>3</v>
@@ -5049,8 +5247,8 @@
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3">
         <v>0</v>
@@ -5079,8 +5277,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5345,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5413,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5481,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5549,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,59 +5617,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E89" s="3">
         <v>7300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1400</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5469,8 +5685,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,8 +5713,9 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5520,8 +5740,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -5559,8 +5779,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5847,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,59 +5915,62 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-52300</v>
+      </c>
+      <c r="E94" s="3">
         <v>53100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>39600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>46500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-39900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-21100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>50300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>27800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-44900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-44600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-116800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-49000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-63000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-55000</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5754,8 +5983,11 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6011,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5800,32 +6033,32 @@
         <v>5200</v>
       </c>
       <c r="I96" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="J96" s="3">
         <v>5100</v>
       </c>
       <c r="K96" s="3">
-        <v>-3700</v>
+        <v>5100</v>
       </c>
       <c r="L96" s="3">
         <v>-3700</v>
       </c>
       <c r="M96" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="N96" s="3">
         <v>-3600</v>
       </c>
       <c r="O96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -5844,8 +6077,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6145,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6213,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,59 +6281,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-47800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-8800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-38800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-24500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>15000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>13800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-43600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-36000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>46700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>81100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>24200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>123700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>34900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>47300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6104,8 +6349,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6130,8 +6378,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6169,59 +6417,62 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E102" s="3">
         <v>12600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-23700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>27300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-21500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>28000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>39400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-56500</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6232,6 +6483,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
   <si>
     <t>SEVN</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,62 +756,65 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E8" s="3">
         <v>8100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>13200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>26100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2000</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,8 +827,11 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -844,41 +851,41 @@
         <v>600</v>
       </c>
       <c r="I9" s="3">
+        <v>600</v>
+      </c>
+      <c r="J9" s="3">
         <v>500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>200</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>8500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>4100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>700</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,62 +898,65 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E10" s="3">
         <v>7500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>9500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>23500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>3300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +969,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,8 +998,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1053,8 +1067,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,8 +1138,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1150,8 +1170,8 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1163,11 +1183,11 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1183,14 +1203,17 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1204,17 +1227,17 @@
         <v>300</v>
       </c>
       <c r="G15" s="3">
+        <v>300</v>
+      </c>
+      <c r="H15" s="3">
         <v>400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -1257,8 +1280,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,8 +1306,9 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1289,53 +1316,53 @@
         <v>3200</v>
       </c>
       <c r="E17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F17" s="3">
         <v>3400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1600</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1348,62 +1375,65 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E18" s="3">
         <v>4900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>6700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>20900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>400</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1446,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,8 +1475,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1471,8 +1505,8 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1495,8 +1529,8 @@
       <c r="S20" s="3">
         <v>0</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1510,38 +1544,41 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E21" s="3">
         <v>5200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>7800</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1551,12 +1588,12 @@
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>21000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,8 +1615,11 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1607,8 +1647,8 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1646,62 +1686,65 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E23" s="3">
         <v>4900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>11200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>21000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1714,8 +1757,11 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1732,11 +1778,11 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -1756,19 +1802,19 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>300</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -1782,8 +1828,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,62 +1899,65 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E26" s="3">
         <v>4900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>20700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,62 +1970,65 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E27" s="3">
         <v>4800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>20700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,8 +2041,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2112,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2122,8 +2183,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2254,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,8 +2325,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2287,8 +2357,8 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2311,8 +2381,8 @@
       <c r="S32" s="3">
         <v>0</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2326,62 +2396,65 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E33" s="3">
         <v>4900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>20700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2394,8 +2467,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,62 +2538,65 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E35" s="3">
         <v>4900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>20700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2530,67 +2609,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2685,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2714,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,62 +2741,63 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E41" s="3">
         <v>70800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>82200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>69600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>93300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>87900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>60400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>81800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>84300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>71100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>76400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>48200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>30400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>46800</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2723,8 +2810,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2791,38 +2881,41 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>657000</v>
+      </c>
+      <c r="E43" s="3">
         <v>605900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>554000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>607800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>587800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>626400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>671800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>628800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>621300</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2853,14 +2946,17 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
+      <c r="W43" s="3">
+        <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2888,8 +2984,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2927,62 +3023,65 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,38 +3094,41 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>700100</v>
+      </c>
+      <c r="E46" s="3">
         <v>677500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>637900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>679900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>682600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>715400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>733400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>712300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>706800</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -3057,14 +3159,17 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
+      <c r="W46" s="3">
+        <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3092,33 +3197,33 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>669900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>695200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>670200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>622700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>572200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>436100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>211400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>147700</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3131,8 +3236,11 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3160,8 +3268,8 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
+      <c r="L48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -3199,8 +3307,11 @@
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3267,8 +3378,11 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3449,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,61 +3520,64 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E52" s="3">
         <v>15300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>16100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15600</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
+      <c r="L52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3">
-        <v>0</v>
-      </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>500</v>
-      </c>
-      <c r="R52" s="3">
-        <v>200</v>
       </c>
       <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
+      <c r="T52" s="3">
+        <v>200</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
@@ -3465,14 +3585,17 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W52" s="3">
-        <v>0</v>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,62 +3662,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>714400</v>
+      </c>
+      <c r="E54" s="3">
         <v>692800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>652600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>694900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>697700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>731500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>750000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>727900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>706800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>746800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>775200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>721700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>635000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>600000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>456200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>244500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>195100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3733,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3762,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,62 +3789,63 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E57" s="3">
         <v>3500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>2100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3727,26 +3858,29 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>244000</v>
+      </c>
+      <c r="E58" s="3">
         <v>255800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>213300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>330300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>333600</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
@@ -3756,14 +3890,14 @@
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -3795,43 +3929,46 @@
       <c r="X58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E59" s="3">
         <v>2300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>1800</v>
       </c>
       <c r="M59" s="3">
         <v>1800</v>
       </c>
       <c r="N59" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="O59" s="3">
         <v>1100</v>
@@ -3840,17 +3977,17 @@
         <v>1100</v>
       </c>
       <c r="Q59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="R59" s="3">
         <v>1700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>700</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3863,38 +4000,41 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>247900</v>
+      </c>
+      <c r="E60" s="3">
         <v>261500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>218400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>334100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>337300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5600</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3925,65 +4065,68 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
+      <c r="W60" s="3">
+        <v>0</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>196400</v>
+      </c>
+      <c r="E61" s="3">
         <v>162000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>162600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>87600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>87500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>454400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>473300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>452700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>433400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>471500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>503500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>452700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>367700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>339600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>215700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>48800</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3999,26 +4142,29 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2100</v>
+      <c r="D62" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F62" s="3">
         <v>2100</v>
       </c>
       <c r="G62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H62" s="3">
         <v>1400</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4028,8 +4174,8 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -4061,14 +4207,17 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
+      <c r="W62" s="3">
+        <v>0</v>
       </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4284,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4355,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,62 +4426,65 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>445500</v>
+      </c>
+      <c r="E66" s="3">
         <v>423500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>383100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>423800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>426200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>460300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>479700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>460100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>439000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>475300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>506800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>455000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>369800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>342300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>219600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>51400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1800</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4339,8 +4497,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4526,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4595,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4666,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4569,8 +4737,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,62 +4808,65 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E72" s="3">
         <v>28800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>29200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>30900</v>
-      </c>
-      <c r="G72" s="3">
-        <v>31800</v>
       </c>
       <c r="H72" s="3">
         <v>31800</v>
       </c>
       <c r="I72" s="3">
+        <v>31800</v>
+      </c>
+      <c r="J72" s="3">
         <v>30900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>28600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>29100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>30000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>28500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>27500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>20100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-600</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
       <c r="S72" s="3">
+        <v>0</v>
+      </c>
+      <c r="T72" s="3">
         <v>400</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4705,8 +4879,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4950,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5021,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,62 +5092,65 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>268900</v>
+      </c>
+      <c r="E76" s="3">
         <v>269300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>269500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>271100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>271600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>271200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>270300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>267800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>267700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>271600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>268400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>266700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>265300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>257700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>236600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>193100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>193200</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4977,8 +5163,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,67 +5234,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,62 +5310,65 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E81" s="3">
         <v>4900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>20700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5186,8 +5381,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,19 +5410,20 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
+      <c r="F83" s="3">
+        <v>300</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>3</v>
@@ -5250,8 +5449,8 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3">
         <v>0</v>
@@ -5280,8 +5479,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5550,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5621,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5692,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5763,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,62 +5834,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E89" s="3">
         <v>3800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5688,8 +5905,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,8 +5934,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5743,8 +5964,8 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -5782,8 +6003,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6074,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,62 +6145,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-49900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-52300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>53100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>39600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>46500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-39900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-21100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>50300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>27800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-44900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-44600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-116800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-49000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-63000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-55000</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5986,8 +6216,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,8 +6245,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6036,32 +6270,32 @@
         <v>5200</v>
       </c>
       <c r="J96" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="K96" s="3">
         <v>5100</v>
       </c>
       <c r="L96" s="3">
-        <v>-3700</v>
+        <v>5100</v>
       </c>
       <c r="M96" s="3">
         <v>-3700</v>
       </c>
       <c r="N96" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="O96" s="3">
         <v>-3600</v>
       </c>
       <c r="P96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-3100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -6080,8 +6314,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6385,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6456,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,62 +6527,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E100" s="3">
         <v>37000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-47800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-38800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-24500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>15000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>13800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-43600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-36000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>46700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>81100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>24200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>123700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>34900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>47300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6352,8 +6598,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6381,8 +6630,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -6420,62 +6669,65 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-29100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-23700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>27300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>28000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>39400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-56500</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6486,6 +6738,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>SEVN</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -759,65 +760,68 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E8" s="3">
         <v>7700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>26100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2000</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -830,8 +834,11 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -854,41 +861,41 @@
         <v>600</v>
       </c>
       <c r="J9" s="3">
+        <v>600</v>
+      </c>
+      <c r="K9" s="3">
         <v>500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3">
         <v>8500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>4100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>700</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -901,65 +908,68 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E10" s="3">
         <v>7200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>7500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>6300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>6900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>8100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>23500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>3300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,8 +1012,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1070,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,8 +1158,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1173,8 +1193,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1186,11 +1206,11 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1206,14 +1226,17 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1230,17 +1253,17 @@
         <v>300</v>
       </c>
       <c r="H15" s="3">
+        <v>300</v>
+      </c>
+      <c r="I15" s="3">
         <v>400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1283,8 +1306,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1307,65 +1333,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>3200</v>
+        <v>3800</v>
       </c>
       <c r="E17" s="3">
         <v>3200</v>
       </c>
       <c r="F17" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G17" s="3">
         <v>3400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1600</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,65 +1405,68 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E18" s="3">
         <v>4500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>6700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>20900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>400</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1449,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,8 +1509,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1508,8 +1542,8 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1532,8 +1566,8 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1547,41 +1581,44 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E21" s="3">
         <v>4800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>4700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7800</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1591,12 +1628,12 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3">
         <v>21000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,8 +1655,11 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1650,8 +1690,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1689,65 +1729,68 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>4500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>4600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>11200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>21000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>400</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1760,8 +1803,11 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1781,11 +1827,11 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -1805,19 +1851,19 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>300</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
+      <c r="U24" s="3">
+        <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
@@ -1831,8 +1877,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1902,65 +1951,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>4500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>6000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>11100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1973,65 +2025,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E27" s="3">
         <v>4500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>6000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>4600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>11100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>20700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2044,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2115,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2186,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2257,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,8 +2395,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2360,8 +2430,8 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2384,8 +2454,8 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2399,65 +2469,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E33" s="3">
         <v>4500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>6000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>4600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>11100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>20700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2541,65 +2617,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E35" s="3">
         <v>4500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>6000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>4600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>11100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>20700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,70 +2691,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2715,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2742,65 +2828,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E41" s="3">
         <v>41600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>70800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>82200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>69600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>93300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>87900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>60400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>81800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>84300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>71100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>76400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>48200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>26200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>19300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>30400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>46800</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,8 +2900,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2884,41 +2974,44 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>625900</v>
+      </c>
+      <c r="E43" s="3">
         <v>657000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>605900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>554000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>607800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>587800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>626400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>671800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>628800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>621300</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -2949,14 +3042,17 @@
       <c r="W43" s="3">
         <v>0</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
+      <c r="X43" s="3">
+        <v>0</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2987,8 +3083,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3026,65 +3122,68 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E45" s="3">
         <v>1400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>2500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3097,41 +3196,44 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>673300</v>
+      </c>
+      <c r="E46" s="3">
         <v>700100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>677500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>637900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>679900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>682600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>715400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>733400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>712300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>706800</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -3162,14 +3264,17 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
+      <c r="X46" s="3">
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3200,33 +3305,33 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>669900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>695200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>670200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>622700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>572200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>436100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>211400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>147700</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3239,8 +3344,11 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3271,8 +3379,8 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N48" s="3">
         <v>0</v>
@@ -3310,8 +3418,11 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3381,8 +3492,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3452,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,64 +3640,67 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E52" s="3">
         <v>14300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>16100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>16600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15600</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>200</v>
       </c>
-      <c r="P52" s="3">
-        <v>0</v>
-      </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>500</v>
-      </c>
-      <c r="S52" s="3">
-        <v>200</v>
       </c>
       <c r="T52" s="3">
         <v>200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>200</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
@@ -3588,14 +3708,17 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3665,65 +3788,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>687400</v>
+      </c>
+      <c r="E54" s="3">
         <v>714400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>692800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>652600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>694900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>697700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>731500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>750000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>727900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>706800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>746800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>775200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>721700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>635000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>600000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>456200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>244500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>195100</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3736,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3763,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3790,65 +3920,66 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>2100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,29 +3992,32 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>236300</v>
+      </c>
+      <c r="E58" s="3">
         <v>244000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>255800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>213300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>330300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>333600</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
@@ -3893,14 +4027,14 @@
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -3932,46 +4066,49 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>1800</v>
       </c>
       <c r="N59" s="3">
         <v>1800</v>
       </c>
       <c r="O59" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="P59" s="3">
         <v>1100</v>
@@ -3980,17 +4117,17 @@
         <v>1100</v>
       </c>
       <c r="R59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="S59" s="3">
         <v>1700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>700</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,41 +4140,44 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>240400</v>
+      </c>
+      <c r="E60" s="3">
         <v>247900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>261500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>218400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>334100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>337300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5600</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -4068,68 +4208,71 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
+      <c r="X60" s="3">
+        <v>0</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>179700</v>
+      </c>
+      <c r="E61" s="3">
         <v>196400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>162000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>162600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>87600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>87500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>454400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>473300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>452700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>433400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>471500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>503500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>452700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>367700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>339600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>215700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>48800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4145,29 +4288,32 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1100</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3">
-        <v>2100</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G62" s="3">
         <v>2100</v>
       </c>
       <c r="H62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="I62" s="3">
         <v>1400</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4323,8 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
@@ -4210,14 +4356,17 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
+      <c r="X62" s="3">
+        <v>0</v>
       </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4287,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4429,65 +4584,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>420400</v>
+      </c>
+      <c r="E66" s="3">
         <v>445500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>423500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>383100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>423800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>426200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>460300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>479700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>460100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>439000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>475300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>506800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>455000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>369800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>342300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>219600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>51400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1800</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4527,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4669,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4740,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4811,65 +4982,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E72" s="3">
         <v>28200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>28800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>29200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>30900</v>
-      </c>
-      <c r="H72" s="3">
-        <v>31800</v>
       </c>
       <c r="I72" s="3">
         <v>31800</v>
       </c>
       <c r="J72" s="3">
+        <v>31800</v>
+      </c>
+      <c r="K72" s="3">
         <v>30900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>28600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>29100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>33100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>30000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>28500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>27500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>20100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-600</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
       <c r="T72" s="3">
+        <v>0</v>
+      </c>
+      <c r="U72" s="3">
         <v>400</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4882,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4953,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5024,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5095,65 +5278,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E76" s="3">
         <v>268900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>269300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>269500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>271100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>271600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>271200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>270300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>267800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>267700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>271600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>268400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>266700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>265300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>257700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>236600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>193100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>193200</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5166,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5237,70 +5426,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5313,65 +5505,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E81" s="3">
         <v>4500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>6000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>4600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>11100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>20700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5384,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5411,22 +5609,23 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
-      </c>
-      <c r="E83" s="3">
-        <v>300</v>
       </c>
       <c r="F83" s="3">
         <v>300</v>
       </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>300</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -5452,8 +5651,8 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P83" s="3">
-        <v>0</v>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q83" s="3">
         <v>0</v>
@@ -5482,8 +5681,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5553,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5624,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5695,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5837,65 +6051,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>4200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>4700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1400</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5908,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5935,8 +6155,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5967,8 +6188,8 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N91" s="3">
         <v>0</v>
@@ -6006,8 +6227,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6077,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6148,65 +6375,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-49900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-52300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>53100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-19100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>39600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>46500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-39900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-21100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>50300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>27800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-44900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-116800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-49000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-63000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-55000</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6219,8 +6449,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6246,8 +6479,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6273,32 +6507,32 @@
         <v>5200</v>
       </c>
       <c r="K96" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="L96" s="3">
         <v>5100</v>
       </c>
       <c r="M96" s="3">
-        <v>-3700</v>
+        <v>5100</v>
       </c>
       <c r="N96" s="3">
         <v>-3700</v>
       </c>
       <c r="O96" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="P96" s="3">
         <v>-3600</v>
       </c>
       <c r="Q96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-3100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
@@ -6317,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6388,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6459,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6530,65 +6773,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="E100" s="3">
         <v>17100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>37000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-47800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-8800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-38800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-24500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>15000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>13800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-43600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-36000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>46700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>81100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>24200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>123700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>34900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>47300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6601,8 +6847,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6633,8 +6882,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6672,65 +6921,68 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-29100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>5400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>27300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>28000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>39400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-56500</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6741,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
   <si>
     <t>SEVN</t>
   </si>
@@ -656,105 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,71 +767,74 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E8" s="3">
         <v>7100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>6500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7700</v>
       </c>
-      <c r="G8" s="3">
-        <v>8100</v>
-      </c>
       <c r="H8" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I8" s="3">
         <v>6900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>7000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>13200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>10500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>15500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>26100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2000</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -844,13 +847,16 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E9" s="3">
         <v>600</v>
@@ -874,41 +880,41 @@
         <v>600</v>
       </c>
       <c r="L9" s="3">
+        <v>600</v>
+      </c>
+      <c r="M9" s="3">
         <v>500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="3">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3">
         <v>8500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>700</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,71 +927,74 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E10" s="3">
         <v>6500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7200</v>
       </c>
-      <c r="G10" s="3">
-        <v>7500</v>
-      </c>
       <c r="H10" s="3">
+        <v>9900</v>
+      </c>
+      <c r="I10" s="3">
         <v>6300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>8200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>23500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1300</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -998,8 +1007,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,8 +1039,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1104,8 +1117,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,8 +1197,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1219,8 +1238,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1232,11 +1251,11 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1252,14 +1271,17 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1282,17 +1304,17 @@
         <v>300</v>
       </c>
       <c r="J15" s="3">
+        <v>300</v>
+      </c>
+      <c r="K15" s="3">
         <v>400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>100</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1335,8 +1357,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,71 +1386,72 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E17" s="3">
         <v>3600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3200</v>
       </c>
       <c r="G17" s="3">
         <v>3200</v>
       </c>
       <c r="H17" s="3">
+        <v>5600</v>
+      </c>
+      <c r="I17" s="3">
         <v>3400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1600</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1438,71 +1464,74 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E18" s="3">
         <v>3400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>2700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>6700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>5200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>11200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>400</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1515,8 +1544,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,8 +1576,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1582,8 +1615,8 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1606,8 +1639,8 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1621,47 +1654,50 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E21" s="3">
         <v>3700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>4600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>4700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7800</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1671,12 +1707,12 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3">
         <v>21000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1734,11 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1736,8 +1775,8 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1775,71 +1814,74 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E23" s="3">
         <v>3400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>11200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>21000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>400</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1852,8 +1894,11 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1879,11 +1924,11 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>-100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
@@ -1903,19 +1948,19 @@
         <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3">
         <v>300</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
         <v>0</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
+      <c r="W24" s="3">
+        <v>0</v>
       </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1974,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,71 +2054,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E26" s="3">
         <v>3400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>20700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2083,71 +2134,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E27" s="3">
         <v>3400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>5200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>20700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2160,8 +2214,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2294,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2374,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2454,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,8 +2534,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2506,8 +2575,8 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P32" s="3">
         <v>0</v>
@@ -2530,8 +2599,8 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2545,71 +2614,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E33" s="3">
         <v>3400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>5200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>20700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2622,8 +2694,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,71 +2774,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E35" s="3">
         <v>3400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>5200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>20700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2776,76 +2854,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2939,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2971,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,71 +3001,72 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>123500</v>
+      </c>
+      <c r="E41" s="3">
         <v>77500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>46000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>70800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>82200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>69600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>93300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>87900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>60400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>81800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>84300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>71100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>76400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>48200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>26200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>19300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>30400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>46800</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2993,8 +3079,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3070,47 +3159,50 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>681300</v>
+      </c>
+      <c r="E43" s="3">
         <v>607000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>625900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>657000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>605900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>554000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>607800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>587800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>626400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>671800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>628800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>621300</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -3141,14 +3233,17 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
+      <c r="Z43" s="3">
+        <v>0</v>
       </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3185,8 +3280,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3224,71 +3319,74 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E45" s="3">
         <v>2500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3301,47 +3399,50 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>806300</v>
+      </c>
+      <c r="E46" s="3">
         <v>687000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>673300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>700100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>677500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>637900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>679900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>682600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>715400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>733400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>712300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>706800</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -3372,14 +3473,17 @@
       <c r="Y46" s="3">
         <v>0</v>
       </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
+      <c r="Z46" s="3">
+        <v>0</v>
       </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3416,33 +3520,33 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>669900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>695200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>670200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>622700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>572200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>436100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>211400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>147700</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3455,8 +3559,11 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3493,8 +3600,8 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O48" s="3">
-        <v>0</v>
+      <c r="O48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P48" s="3">
         <v>0</v>
@@ -3532,8 +3639,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3609,8 +3719,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3799,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,70 +3879,73 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E52" s="3">
         <v>13800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>16100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15600</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="3">
-        <v>0</v>
+      <c r="O52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="R52" s="3">
-        <v>0</v>
-      </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>500</v>
-      </c>
-      <c r="U52" s="3">
-        <v>200</v>
       </c>
       <c r="V52" s="3">
         <v>200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
+      <c r="W52" s="3">
+        <v>200</v>
       </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
@@ -3834,14 +3953,17 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,71 +4039,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>820900</v>
+      </c>
+      <c r="E54" s="3">
         <v>700800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>687400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>714400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>692800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>652600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>694900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>697700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>731500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>750000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>727900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>706800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>746800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>775200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>721700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>635000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>600000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>456200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>244500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>195100</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4119,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4151,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,71 +4181,72 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2600</v>
       </c>
-      <c r="G57" s="3">
-        <v>3500</v>
-      </c>
       <c r="H57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="I57" s="3">
         <v>2700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4129,35 +4259,38 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>217100</v>
+        <v>135400</v>
       </c>
       <c r="E58" s="3">
+        <v>352400</v>
+      </c>
+      <c r="F58" s="3">
         <v>236300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>244000</v>
       </c>
-      <c r="G58" s="3">
-        <v>255800</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>213300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>330300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>333600</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4167,14 +4300,14 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -4206,52 +4339,55 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E59" s="3">
         <v>2000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2400</v>
-      </c>
-      <c r="O59" s="3">
-        <v>1800</v>
       </c>
       <c r="P59" s="3">
         <v>1800</v>
       </c>
       <c r="Q59" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="R59" s="3">
         <v>1100</v>
@@ -4260,17 +4396,17 @@
         <v>1100</v>
       </c>
       <c r="T59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U59" s="3">
         <v>1700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>700</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4283,47 +4419,50 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>221700</v>
+        <v>139700</v>
       </c>
       <c r="E60" s="3">
+        <v>357000</v>
+      </c>
+      <c r="F60" s="3">
         <v>240400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>247900</v>
       </c>
-      <c r="G60" s="3">
-        <v>261500</v>
-      </c>
       <c r="H60" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I60" s="3">
         <v>218400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>334100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>337300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5600</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -4354,74 +4493,77 @@
       <c r="Y60" s="3">
         <v>0</v>
       </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
+      <c r="Z60" s="3">
+        <v>0</v>
       </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>212400</v>
+        <v>352200</v>
       </c>
       <c r="E61" s="3">
+        <v>77000</v>
+      </c>
+      <c r="F61" s="3">
         <v>179700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>196400</v>
       </c>
-      <c r="G61" s="3">
-        <v>162000</v>
-      </c>
       <c r="H61" s="3">
+        <v>417800</v>
+      </c>
+      <c r="I61" s="3">
         <v>162600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>87600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>87500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>454400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>473300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>452700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>433400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>471500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>503500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>452700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>367700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>339600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>215700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>48800</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4437,8 +4579,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4449,23 +4594,23 @@
         <v>300</v>
       </c>
       <c r="F62" s="3">
+        <v>300</v>
+      </c>
+      <c r="G62" s="3">
         <v>1100</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H62" s="3">
-        <v>2100</v>
+        <v>800</v>
       </c>
       <c r="I62" s="3">
         <v>2100</v>
       </c>
       <c r="J62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="K62" s="3">
         <v>1400</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4475,8 +4620,8 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -4508,14 +4653,17 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
+      <c r="Z62" s="3">
+        <v>0</v>
       </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4739,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4819,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,71 +4899,74 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>492200</v>
+      </c>
+      <c r="E66" s="3">
         <v>434400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>420400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>445500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>423500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>383100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>423800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>426200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>460300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>479700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>460100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>439000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>475300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>506800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>455000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>369800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>342300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>219600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>51400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1800</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4822,8 +4979,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5011,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5089,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,8 +5169,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5082,8 +5249,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,71 +5329,74 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E72" s="3">
         <v>24900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>25600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>28200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>29200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>30900</v>
-      </c>
-      <c r="J72" s="3">
-        <v>31800</v>
       </c>
       <c r="K72" s="3">
         <v>31800</v>
       </c>
       <c r="L72" s="3">
+        <v>31800</v>
+      </c>
+      <c r="M72" s="3">
         <v>30900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>28600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>29100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>33100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>30000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>28500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>27500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>20100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-600</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
       <c r="V72" s="3">
+        <v>0</v>
+      </c>
+      <c r="W72" s="3">
         <v>400</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5236,8 +5409,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5489,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5569,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,71 +5649,74 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>328700</v>
+      </c>
+      <c r="E76" s="3">
         <v>266500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>267000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>268900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>269300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>269500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>271100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>271600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>271200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>270300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>267800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>267700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>271600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>268400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>266700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>265300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>257700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>236600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>193100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>193200</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5544,8 +5729,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,76 +5809,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,71 +5894,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E81" s="3">
         <v>3400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>5200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>20700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5780,8 +5974,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,8 +6006,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5821,16 +6019,16 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
+        <v>300</v>
+      </c>
+      <c r="G83" s="3">
         <v>400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>300</v>
       </c>
       <c r="H83" s="3">
         <v>300</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+      <c r="I83" s="3">
+        <v>300</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
@@ -5856,8 +6054,8 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="R83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -5886,8 +6084,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6164,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6244,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6324,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6404,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,8 +6484,11 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -6280,62 +6496,62 @@
         <v>3200</v>
       </c>
       <c r="E89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="F89" s="3">
         <v>5000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>4200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>5300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1400</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6348,8 +6564,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,8 +6596,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6415,8 +6635,8 @@
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P91" s="3">
         <v>0</v>
@@ -6454,8 +6674,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6754,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,71 +6834,74 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-72600</v>
+      </c>
+      <c r="E94" s="3">
         <v>20100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>29500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-49900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-52300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>53100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>39600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>46500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-39900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-21100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>50300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>27800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-44900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-44600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-116800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-49000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-63000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-55000</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6685,8 +6914,11 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6946,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6723,7 +6956,7 @@
         <v>4200</v>
       </c>
       <c r="E96" s="3">
-        <v>5200</v>
+        <v>4200</v>
       </c>
       <c r="F96" s="3">
         <v>5200</v>
@@ -6747,32 +6980,32 @@
         <v>5200</v>
       </c>
       <c r="M96" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="N96" s="3">
         <v>5100</v>
       </c>
       <c r="O96" s="3">
-        <v>-3700</v>
+        <v>5100</v>
       </c>
       <c r="P96" s="3">
         <v>-3700</v>
       </c>
       <c r="Q96" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="R96" s="3">
         <v>-3600</v>
       </c>
       <c r="S96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-3100</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -6791,8 +7024,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7104,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7184,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,71 +7264,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E100" s="3">
         <v>8300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>17100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>37000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-47800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-8800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-38800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-24500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>15000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>13800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-43600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-36000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>46700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>81100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>24200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>123700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>34900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>47300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7099,8 +7344,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7137,8 +7385,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -7176,71 +7424,74 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E102" s="3">
         <v>31500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-29100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-23700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>27300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-21500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>28000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>39400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-16500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-56500</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7251,6 +7502,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SEVN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="92">
   <si>
     <t>SEVN</t>
   </si>
@@ -656,108 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -770,74 +771,77 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E8" s="3">
         <v>7900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>10500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>16700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>10500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>15500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>26100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2000</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -850,16 +854,19 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>600</v>
+      </c>
+      <c r="E9" s="3">
         <v>500</v>
-      </c>
-      <c r="E9" s="3">
-        <v>600</v>
       </c>
       <c r="F9" s="3">
         <v>600</v>
@@ -883,41 +890,41 @@
         <v>600</v>
       </c>
       <c r="M9" s="3">
+        <v>600</v>
+      </c>
+      <c r="N9" s="3">
         <v>500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3">
         <v>8500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>6500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>700</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -930,74 +937,77 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E10" s="3">
         <v>7400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>6500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>6300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>6900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>8200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>23500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1300</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1010,8 +1020,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,8 +1053,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1120,8 +1134,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1200,8 +1217,11 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1241,8 +1261,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1254,11 +1274,11 @@
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1274,14 +1294,17 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1307,17 +1330,17 @@
         <v>300</v>
       </c>
       <c r="K15" s="3">
+        <v>300</v>
+      </c>
+      <c r="L15" s="3">
         <v>400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>100</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
@@ -1360,8 +1383,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1387,74 +1413,75 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E17" s="3">
         <v>3100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1600</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1467,74 +1494,77 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E18" s="3">
         <v>4800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>6700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>5200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>11200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,8 +1577,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1577,8 +1610,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1618,8 +1652,8 @@
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1642,8 +1676,8 @@
       <c r="W20" s="3">
         <v>0</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
+      <c r="X20" s="3">
+        <v>0</v>
       </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
@@ -1657,50 +1691,53 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E21" s="3">
         <v>5100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>4600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>7800</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1710,12 +1747,12 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T21" s="3">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>21000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,8 +1774,11 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1778,8 +1818,8 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1817,74 +1857,77 @@
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E23" s="3">
         <v>4800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>6800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>11200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>21000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>400</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1897,8 +1940,11 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1927,11 +1973,11 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>-100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
@@ -1951,19 +1997,19 @@
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>300</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
+      <c r="X24" s="3">
+        <v>0</v>
       </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
@@ -1977,8 +2023,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2057,74 +2106,77 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E26" s="3">
         <v>4800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>6000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>11100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>20700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>400</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2137,74 +2189,77 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E27" s="3">
         <v>4700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>5200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>11100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>20700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2217,8 +2272,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2297,8 +2355,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2377,8 +2438,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2457,8 +2521,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2537,8 +2604,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2578,8 +2648,8 @@
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -2602,8 +2672,8 @@
       <c r="W32" s="3">
         <v>0</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
+      <c r="X32" s="3">
+        <v>0</v>
       </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
@@ -2617,74 +2687,77 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E33" s="3">
         <v>4800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>5200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>11100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>20700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2697,8 +2770,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2777,74 +2853,77 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E35" s="3">
         <v>4800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>5200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>11100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>20700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2857,79 +2936,82 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2942,8 +3024,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2972,8 +3057,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3002,74 +3088,75 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>56600</v>
+      </c>
+      <c r="E41" s="3">
         <v>123500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>77500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>46000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>70800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>82200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>69600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>93300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>87900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>60400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>81800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>71100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>76400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>48200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>26200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>19300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>30400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>46800</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3082,8 +3169,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3162,50 +3252,53 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>725200</v>
+      </c>
+      <c r="E43" s="3">
         <v>681300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>607000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>625900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>657000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>605900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>554000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>607800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>587800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>626400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>671800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>628800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>621300</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -3236,14 +3329,17 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
+      <c r="AA43" s="3">
+        <v>0</v>
       </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3283,8 +3379,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3322,74 +3418,77 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
         <v>1600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3402,50 +3501,53 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>783200</v>
+      </c>
+      <c r="E46" s="3">
         <v>806300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>687000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>673300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>700100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>677500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>637900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>679900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>682600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>715400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>733400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>712300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>706800</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3476,14 +3578,17 @@
       <c r="Z46" s="3">
         <v>0</v>
       </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
+      <c r="AA46" s="3">
+        <v>0</v>
       </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3523,33 +3628,33 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>669900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>695200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>670200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>622700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>572200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>436100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>211400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>147700</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3562,8 +3667,11 @@
       <c r="AB47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3603,8 +3711,8 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P48" s="3">
-        <v>0</v>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q48" s="3">
         <v>0</v>
@@ -3642,8 +3750,11 @@
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3722,8 +3833,11 @@
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3802,8 +3916,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3882,73 +3999,76 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E52" s="3">
         <v>14500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>16100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>16600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15600</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>200</v>
       </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
       <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>500</v>
-      </c>
-      <c r="V52" s="3">
-        <v>200</v>
       </c>
       <c r="W52" s="3">
         <v>200</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
+      <c r="X52" s="3">
+        <v>200</v>
       </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
@@ -3956,14 +4076,17 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4042,74 +4165,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>797400</v>
+      </c>
+      <c r="E54" s="3">
         <v>820900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>700800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>687400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>714400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>692800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>652600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>694900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>697700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>731500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>750000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>727900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>706800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>746800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>775200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>721700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>635000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>600000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>456200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>244500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>195100</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4122,8 +4248,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4152,8 +4281,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4182,74 +4312,75 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E57" s="3">
         <v>2500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2200</v>
-      </c>
-      <c r="G57" s="3">
-        <v>2600</v>
       </c>
       <c r="H57" s="3">
         <v>2600</v>
       </c>
       <c r="I57" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J57" s="3">
         <v>2700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4262,38 +4393,41 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>135400</v>
+        <v>135500</v>
       </c>
       <c r="E58" s="3">
+        <v>423200</v>
+      </c>
+      <c r="F58" s="3">
         <v>352400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>236300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>244000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>213300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>330300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>333600</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4303,14 +4437,14 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
+      <c r="P58" s="3">
+        <v>0</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -4342,55 +4476,58 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2400</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1800</v>
       </c>
       <c r="Q59" s="3">
         <v>1800</v>
       </c>
       <c r="R59" s="3">
-        <v>1100</v>
+        <v>1800</v>
       </c>
       <c r="S59" s="3">
         <v>1100</v>
@@ -4399,17 +4536,17 @@
         <v>1100</v>
       </c>
       <c r="U59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="V59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>700</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4422,50 +4559,53 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>139700</v>
+        <v>139900</v>
       </c>
       <c r="E60" s="3">
+        <v>427500</v>
+      </c>
+      <c r="F60" s="3">
         <v>357000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>240400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>247900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>218400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>334100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>337300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5600</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4496,77 +4636,80 @@
       <c r="Z60" s="3">
         <v>0</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
+      <c r="AA60" s="3">
+        <v>0</v>
       </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>352200</v>
+        <v>330300</v>
       </c>
       <c r="E61" s="3">
+        <v>64400</v>
+      </c>
+      <c r="F61" s="3">
         <v>77000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>179700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>196400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>417800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>162600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>87600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>87500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>454400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>473300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>452700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>433400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>471500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>503500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>452700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>367700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>339600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>215700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>48800</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4582,13 +4725,16 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E62" s="3">
         <v>300</v>
@@ -4597,23 +4743,23 @@
         <v>300</v>
       </c>
       <c r="G62" s="3">
+        <v>300</v>
+      </c>
+      <c r="H62" s="3">
         <v>1100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>2100</v>
       </c>
       <c r="J62" s="3">
         <v>2100</v>
       </c>
       <c r="K62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="L62" s="3">
         <v>1400</v>
       </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4623,8 +4769,8 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q62" s="3">
         <v>0</v>
@@ -4656,14 +4802,17 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-      <c r="AA62" s="3" t="s">
-        <v>3</v>
+      <c r="AA62" s="3">
+        <v>0</v>
       </c>
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4742,8 +4891,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4822,8 +4974,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4902,74 +5057,77 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>470400</v>
+      </c>
+      <c r="E66" s="3">
         <v>492200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>434400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>420400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>445500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>423500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>383100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>423800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>426200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>460300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>479700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>460100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>439000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>475300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>506800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>455000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>369800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>342300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>219600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>51400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1800</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4982,8 +5140,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5012,8 +5173,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5092,8 +5254,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5172,8 +5337,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5252,8 +5420,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5332,74 +5503,77 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E72" s="3">
         <v>25400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>24900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>25600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>28200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>28800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>29200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>30900</v>
-      </c>
-      <c r="K72" s="3">
-        <v>31800</v>
       </c>
       <c r="L72" s="3">
         <v>31800</v>
       </c>
       <c r="M72" s="3">
+        <v>31800</v>
+      </c>
+      <c r="N72" s="3">
         <v>30900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>28600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>29100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>33100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>30000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>28500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>27500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>20100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-600</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
       <c r="W72" s="3">
+        <v>0</v>
+      </c>
+      <c r="X72" s="3">
         <v>400</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5412,8 +5586,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5492,8 +5669,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5572,8 +5752,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5652,74 +5835,77 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E76" s="3">
         <v>328700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>266500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>267000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>268900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>269300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>269500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>271100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>271600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>271200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>270300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>267800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>267700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>271600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>268400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>266700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>265300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>257700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>236600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>193100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>193200</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5732,8 +5918,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5812,79 +6001,82 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5897,74 +6089,77 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E81" s="3">
         <v>4800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>5200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>11100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>20700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5977,8 +6172,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6007,8 +6205,9 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6022,16 +6221,16 @@
         <v>300</v>
       </c>
       <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
         <v>400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>300</v>
       </c>
       <c r="I83" s="3">
         <v>300</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>300</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -6057,8 +6256,8 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T83" s="3">
         <v>0</v>
@@ -6087,8 +6286,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6167,8 +6369,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6247,8 +6452,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6327,8 +6535,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6407,8 +6618,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6487,74 +6701,77 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3200</v>
+        <v>5000</v>
       </c>
       <c r="E89" s="3">
         <v>3200</v>
       </c>
       <c r="F89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="G89" s="3">
         <v>5000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-1400</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6567,8 +6784,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6597,8 +6817,9 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6638,8 +6859,8 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -6677,8 +6898,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6757,8 +6981,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6837,74 +7064,77 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-72600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>20100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>29500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-49900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-52300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>53100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>39600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>46500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-39900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-21100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>50300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>27800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-22400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-44900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-44600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-116800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-49000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-63000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-55000</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6917,8 +7147,11 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6947,19 +7180,20 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>4200</v>
+        <v>6300</v>
       </c>
       <c r="E96" s="3">
         <v>4200</v>
       </c>
       <c r="F96" s="3">
-        <v>5200</v>
+        <v>4200</v>
       </c>
       <c r="G96" s="3">
         <v>5200</v>
@@ -6983,32 +7217,32 @@
         <v>5200</v>
       </c>
       <c r="N96" s="3">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="O96" s="3">
         <v>5100</v>
       </c>
       <c r="P96" s="3">
-        <v>-3700</v>
+        <v>5100</v>
       </c>
       <c r="Q96" s="3">
         <v>-3700</v>
       </c>
       <c r="R96" s="3">
-        <v>-3600</v>
+        <v>-3700</v>
       </c>
       <c r="S96" s="3">
         <v>-3600</v>
       </c>
       <c r="T96" s="3">
-        <v>0</v>
+        <v>-3600</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-3100</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
         <v>0</v>
       </c>
@@ -7027,8 +7261,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7107,8 +7344,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7187,8 +7427,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7267,74 +7510,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-28300</v>
+      </c>
+      <c r="E100" s="3">
         <v>115400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>17100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>37000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-47800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-8800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-38800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-24500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>15000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>13800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-43600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>46700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>81100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>24200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>123700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>34900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>47300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7347,8 +7593,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7388,8 +7637,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -7427,74 +7676,77 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-66900</v>
+      </c>
+      <c r="E102" s="3">
         <v>46000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>31500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-29100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-23700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>27300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>28000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>39400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-10800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-56500</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7505,6 +7757,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
